--- a/Zagentexecution/incidents/xml_payment_structured_address/original_marlies/XML Address un structured.xlsx
+++ b/Zagentexecution/incidents/xml_payment_structured_address/original_marlies/XML Address un structured.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unesco-my.sharepoint.com/personal/m_spronk_unesco_org/Documents/Documents/BFM/Payment/XML unstructured address/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jp_lopez\projects\abapobjectscreation\Zagentexecution\incidents\xml_payment_structured_address\original_marlies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="8_{3A60821A-1C94-4C33-B40D-BCE6C16B15EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D45CB49E-B44B-49A1-99DB-6D70DBE9DEE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C106DFDE-E699-4F3F-AF20-3D3A3C45EA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{3F3F14F8-0D6B-4928-BB18-5462DC714B35}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{3F3F14F8-0D6B-4928-BB18-5462DC714B35}"/>
   </bookViews>
   <sheets>
     <sheet name="File analysis" sheetId="1" r:id="rId1"/>
     <sheet name="SEPA XML" sheetId="3" r:id="rId2"/>
+    <sheet name="File Analysis2" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File analysis'!$A$1:$R$9</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="102">
   <si>
     <t>CITI XML</t>
   </si>
@@ -1002,6 +1003,47 @@
   </si>
   <si>
     <t>Postal code is missing; to review if this is related to master data or to type of payment</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>Cases</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>Correct, no need to change
+Pay attention to AdrLine: in this case it's a part of the name, 2nd line of name (vendor 904874) 
+*******How should a long name, exceeding allowed characters, being interpreted?</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Current Outcome</t>
+  </si>
+  <si>
+    <t>New Suggeted Outcome</t>
+  </si>
+  <si>
+    <t>Streetname/nr, postal code and city should be in designated tabs. No longer entries in Adrline To verify if this tag is using Adrline. To test with a vendor and alternative payee</t>
+  </si>
+  <si>
+    <t>Streetname/nr, postal code and city should be in designated tabs. No longer entries in Adrline To verify if this tag is using Adrline To test with a vendor and alternative payee</t>
+  </si>
+  <si>
+    <t>Streetname/nr, postal code and city should be in designated tabs. No longer entries in Adrline To verify if this tag is using Adrline</t>
+  </si>
+  <si>
+    <t>Remarks suggestion</t>
   </si>
 </sst>
 </file>
@@ -1059,15 +1101,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1075,11 +1129,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1093,11 +1162,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1434,569 +1536,569 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A85FC0-83B2-4B0D-ABEE-C70DE68F7911}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="45.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.36328125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="45.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:18" ht="116" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:18" ht="116" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="120" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:18" ht="116" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="240" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:18" ht="232" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="225" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:18" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="195" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="165" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:18" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="O9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="135" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="O10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="O11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q11" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="120" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:18" ht="116" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="9" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2009,31 +2111,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545B15EE-07F5-45F5-9185-3FD8586F0DCC}">
   <dimension ref="A1:S4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="45.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="39.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="45.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="39.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.81640625" style="1" customWidth="1"/>
     <col min="16" max="16" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="37.140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37.1796875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2092,7 +2194,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -2142,7 +2244,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -2192,7 +2294,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="145" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -2244,6 +2346,1413 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:S3" xr:uid="{A4A85FC0-83B2-4B0D-ABEE-C70DE68F7911}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3DD3004-D26C-4B54-9551-9FA6139458FB}">
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.08984375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.08984375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.90625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+    </row>
+    <row r="10" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" ht="116" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" ht="203" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" ht="174" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:11" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11" ht="145" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11" ht="174" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11" ht="145" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:11" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:11" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+    </row>
+    <row r="39" spans="1:11" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:11" ht="116" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+    </row>
+    <row r="42" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+    </row>
+    <row r="43" spans="1:11" ht="116" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+    </row>
+    <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
